--- a/data/output/2025/evaluasi_91.xlsx
+++ b/data/output/2025/evaluasi_91.xlsx
@@ -2522,7 +2522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,6 +2778,286 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.872671147935458</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>46.95836142521652</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.22919542371486</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.169865726136402</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-8.734290497650441</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.052124952212898</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.005762156869684529</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1415846490194133</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6.260736386759404</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9103</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.292529585366893</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2792,7 +3072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3034,20 +3314,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.645031197710759</v>
+        <v>35.99944864732349</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3062,18 +3342,298 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3.098215506116428</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.616951747905258</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.741539346507634</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.09998412495764919</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8036472319897789</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.539768271636062</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7.919643314709536</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.564070068218874</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.397196475845917</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.645031197710759</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9104</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Teluk Bintuni</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>-2.731258646359957</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3090,7 +3650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3290,6 +3850,286 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.247306935518624</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.447925908456816</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.296189463747475</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.83275584586611</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1466099365100569</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4589190309877199</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.07924139305722377</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.138593525214141</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.756164903924795</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9105</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1562161243206271</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3304,7 +4144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3546,20 +4386,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.06544267318656</v>
+        <v>8.988300312081893</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3574,18 +4414,326 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>43.91826462380878</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.617485483258288</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.3246954986287</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8.917934898765182</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.519152832698277</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6182350597152051</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.095048370824086</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.192240926819061</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2.102561318974525</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6.753839694485414</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.06544267318656</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9111</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Manokwari Selatan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>-2.152733000885108</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3602,7 +4750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3998,6 +5146,258 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>40.63227163543738</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.592301809862303</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.457970593568516</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.039106809647123</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.014717436408959</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.774936906968192</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6.593194160674365</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.8892323212322</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9102</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaimana</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.805289511928049</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4012,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4282,18 +5682,354 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>51.62789095031997</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.438066760050105</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.34658219274512</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.536043542715434</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.244595085877845</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2644398277368694</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.313567374522867</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.921940588279391</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.913262257874596</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7.099112055639481</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.656083334790643</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6858677815624046</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9112</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Arfak</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>3.932239392774851</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4310,7 +6046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4373,6 +6109,286 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.860821771877047</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>38.03625781021081</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.189002661776982</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.40113318990792</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.174500286876934</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.7309876525396772</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.794422330775049</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1336592874502761</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.792212099865475</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Fakfak</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.138669538466514</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
